--- a/output/mexico_demanda_nacional_daily.xlsx
+++ b/output/mexico_demanda_nacional_daily.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,6 +644,486 @@
         <v>680647.8</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>42410</v>
+      </c>
+      <c r="B16" t="n">
+        <v>683822.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>42411</v>
+      </c>
+      <c r="B17" t="n">
+        <v>682102.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>42412</v>
+      </c>
+      <c r="B18" t="n">
+        <v>683605.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>42413</v>
+      </c>
+      <c r="B19" t="n">
+        <v>655595.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>42414</v>
+      </c>
+      <c r="B20" t="n">
+        <v>591920.1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>42415</v>
+      </c>
+      <c r="B21" t="n">
+        <v>591920.1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>42416</v>
+      </c>
+      <c r="B22" t="n">
+        <v>591920.1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>42417</v>
+      </c>
+      <c r="B23" t="n">
+        <v>702820.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>42418</v>
+      </c>
+      <c r="B24" t="n">
+        <v>708946.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>42419</v>
+      </c>
+      <c r="B25" t="n">
+        <v>711094.9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>42420</v>
+      </c>
+      <c r="B26" t="n">
+        <v>679600.6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>42421</v>
+      </c>
+      <c r="B27" t="n">
+        <v>621470.6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>42422</v>
+      </c>
+      <c r="B28" t="n">
+        <v>700892.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>42423</v>
+      </c>
+      <c r="B29" t="n">
+        <v>721756.6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>42424</v>
+      </c>
+      <c r="B30" t="n">
+        <v>713395.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>42425</v>
+      </c>
+      <c r="B31" t="n">
+        <v>704595.6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>42426</v>
+      </c>
+      <c r="B32" t="n">
+        <v>698502.8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>42427</v>
+      </c>
+      <c r="B33" t="n">
+        <v>664560.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>42428</v>
+      </c>
+      <c r="B34" t="n">
+        <v>598881.7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>42429</v>
+      </c>
+      <c r="B35" t="n">
+        <v>685388.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>42430</v>
+      </c>
+      <c r="B36" t="n">
+        <v>715356.9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>42431</v>
+      </c>
+      <c r="B37" t="n">
+        <v>720821.1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>42432</v>
+      </c>
+      <c r="B38" t="n">
+        <v>724105.1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>42433</v>
+      </c>
+      <c r="B39" t="n">
+        <v>720381.9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>42434</v>
+      </c>
+      <c r="B40" t="n">
+        <v>684547.2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>42435</v>
+      </c>
+      <c r="B41" t="n">
+        <v>620319.3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>42436</v>
+      </c>
+      <c r="B42" t="n">
+        <v>701493.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42437</v>
+      </c>
+      <c r="B43" t="n">
+        <v>713604.2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>42438</v>
+      </c>
+      <c r="B44" t="n">
+        <v>691262.5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>42439</v>
+      </c>
+      <c r="B45" t="n">
+        <v>684334.6</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>42440</v>
+      </c>
+      <c r="B46" t="n">
+        <v>695941</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>42441</v>
+      </c>
+      <c r="B47" t="n">
+        <v>672403.8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>42442</v>
+      </c>
+      <c r="B48" t="n">
+        <v>620115</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>42443</v>
+      </c>
+      <c r="B49" t="n">
+        <v>711788.5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>42444</v>
+      </c>
+      <c r="B50" t="n">
+        <v>739646.7</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>42445</v>
+      </c>
+      <c r="B51" t="n">
+        <v>750463.9</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>42446</v>
+      </c>
+      <c r="B52" t="n">
+        <v>752959.2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>42447</v>
+      </c>
+      <c r="B53" t="n">
+        <v>753802.6</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>42448</v>
+      </c>
+      <c r="B54" t="n">
+        <v>705462.4</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>42449</v>
+      </c>
+      <c r="B55" t="n">
+        <v>622167.3</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>42450</v>
+      </c>
+      <c r="B56" t="n">
+        <v>641141.8</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>42451</v>
+      </c>
+      <c r="B57" t="n">
+        <v>684561.1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>42452</v>
+      </c>
+      <c r="B58" t="n">
+        <v>710387.7</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>42453</v>
+      </c>
+      <c r="B59" t="n">
+        <v>669771.8</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>42454</v>
+      </c>
+      <c r="B60" t="n">
+        <v>601875.1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>42455</v>
+      </c>
+      <c r="B61" t="n">
+        <v>617332.3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>42456</v>
+      </c>
+      <c r="B62" t="n">
+        <v>618562</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>42457</v>
+      </c>
+      <c r="B63" t="n">
+        <v>727967.3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>42458</v>
+      </c>
+      <c r="B64" t="n">
+        <v>754843.7</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>42459</v>
+      </c>
+      <c r="B65" t="n">
+        <v>770034.3</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>42460</v>
+      </c>
+      <c r="B66" t="n">
+        <v>775583.8</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>42461</v>
+      </c>
+      <c r="B67" t="n">
+        <v>765960.8</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>42462</v>
+      </c>
+      <c r="B68" t="n">
+        <v>717383</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>42463</v>
+      </c>
+      <c r="B69" t="n">
+        <v>616028.8</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>42464</v>
+      </c>
+      <c r="B70" t="n">
+        <v>727032.6</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>42465</v>
+      </c>
+      <c r="B71" t="n">
+        <v>756406</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>42466</v>
+      </c>
+      <c r="B72" t="n">
+        <v>765200.4</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>42467</v>
+      </c>
+      <c r="B73" t="n">
+        <v>775285.3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>42468</v>
+      </c>
+      <c r="B74" t="n">
+        <v>773628.3</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>42469</v>
+      </c>
+      <c r="B75" t="n">
+        <v>731798.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/mexico_demanda_nacional_daily.xlsx
+++ b/output/mexico_demanda_nacional_daily.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B75"/>
+  <dimension ref="A1:B135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,486 @@
         <v>731798.7</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>42470</v>
+      </c>
+      <c r="B76" t="n">
+        <v>669043.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>42471</v>
+      </c>
+      <c r="B77" t="n">
+        <v>767779.8</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>42472</v>
+      </c>
+      <c r="B78" t="n">
+        <v>795631.8</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>42473</v>
+      </c>
+      <c r="B79" t="n">
+        <v>793304.3</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>42474</v>
+      </c>
+      <c r="B80" t="n">
+        <v>794734.3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>42475</v>
+      </c>
+      <c r="B81" t="n">
+        <v>787328.3</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>42476</v>
+      </c>
+      <c r="B82" t="n">
+        <v>753619.9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>42477</v>
+      </c>
+      <c r="B83" t="n">
+        <v>694608.2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>42478</v>
+      </c>
+      <c r="B84" t="n">
+        <v>782335.9</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>42479</v>
+      </c>
+      <c r="B85" t="n">
+        <v>784061.2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>42480</v>
+      </c>
+      <c r="B86" t="n">
+        <v>785143.9</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>42481</v>
+      </c>
+      <c r="B87" t="n">
+        <v>787479.1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>42482</v>
+      </c>
+      <c r="B88" t="n">
+        <v>788780.8</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>42483</v>
+      </c>
+      <c r="B89" t="n">
+        <v>742754.4</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>42484</v>
+      </c>
+      <c r="B90" t="n">
+        <v>676873.3</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>42485</v>
+      </c>
+      <c r="B91" t="n">
+        <v>778161.5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>42486</v>
+      </c>
+      <c r="B92" t="n">
+        <v>805895.1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>42487</v>
+      </c>
+      <c r="B93" t="n">
+        <v>810686.3</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>42488</v>
+      </c>
+      <c r="B94" t="n">
+        <v>816971.5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>42489</v>
+      </c>
+      <c r="B95" t="n">
+        <v>816949.8</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>42490</v>
+      </c>
+      <c r="B96" t="n">
+        <v>764145.8</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>42491</v>
+      </c>
+      <c r="B97" t="n">
+        <v>764145.8</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>42492</v>
+      </c>
+      <c r="B98" t="n">
+        <v>770596.2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>42493</v>
+      </c>
+      <c r="B99" t="n">
+        <v>792937.9</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>42494</v>
+      </c>
+      <c r="B100" t="n">
+        <v>803816.5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>42495</v>
+      </c>
+      <c r="B101" t="n">
+        <v>797771.3</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>42496</v>
+      </c>
+      <c r="B102" t="n">
+        <v>806238.5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>42497</v>
+      </c>
+      <c r="B103" t="n">
+        <v>763324.4</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>42498</v>
+      </c>
+      <c r="B104" t="n">
+        <v>702611.3</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>42499</v>
+      </c>
+      <c r="B105" t="n">
+        <v>789186.4</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>42500</v>
+      </c>
+      <c r="B106" t="n">
+        <v>795184.2</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>42501</v>
+      </c>
+      <c r="B107" t="n">
+        <v>838274.1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>42502</v>
+      </c>
+      <c r="B108" t="n">
+        <v>848156.5</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>42503</v>
+      </c>
+      <c r="B109" t="n">
+        <v>842298</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>42504</v>
+      </c>
+      <c r="B110" t="n">
+        <v>798310.2</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>42505</v>
+      </c>
+      <c r="B111" t="n">
+        <v>721688.2</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>42506</v>
+      </c>
+      <c r="B112" t="n">
+        <v>807143</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>42507</v>
+      </c>
+      <c r="B113" t="n">
+        <v>845137.4</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>42508</v>
+      </c>
+      <c r="B114" t="n">
+        <v>841274.9</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>42509</v>
+      </c>
+      <c r="B115" t="n">
+        <v>842501.9</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>42510</v>
+      </c>
+      <c r="B116" t="n">
+        <v>843808.6</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>42511</v>
+      </c>
+      <c r="B117" t="n">
+        <v>812141</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>42512</v>
+      </c>
+      <c r="B118" t="n">
+        <v>749231.9</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>42513</v>
+      </c>
+      <c r="B119" t="n">
+        <v>848264.9</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>42514</v>
+      </c>
+      <c r="B120" t="n">
+        <v>866316.4</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>42515</v>
+      </c>
+      <c r="B121" t="n">
+        <v>874266.7</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>42516</v>
+      </c>
+      <c r="B122" t="n">
+        <v>862004.3</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>42517</v>
+      </c>
+      <c r="B123" t="n">
+        <v>855833.4</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>42518</v>
+      </c>
+      <c r="B124" t="n">
+        <v>820620.1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>42519</v>
+      </c>
+      <c r="B125" t="n">
+        <v>753520.2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>42520</v>
+      </c>
+      <c r="B126" t="n">
+        <v>840554.7</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>42521</v>
+      </c>
+      <c r="B127" t="n">
+        <v>858519.6</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>42522</v>
+      </c>
+      <c r="B128" t="n">
+        <v>839946.4</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>42523</v>
+      </c>
+      <c r="B129" t="n">
+        <v>840224.6</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>42524</v>
+      </c>
+      <c r="B130" t="n">
+        <v>847772.7</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>42525</v>
+      </c>
+      <c r="B131" t="n">
+        <v>815139.1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>42526</v>
+      </c>
+      <c r="B132" t="n">
+        <v>740453.3</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>42527</v>
+      </c>
+      <c r="B133" t="n">
+        <v>828743.5</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>42528</v>
+      </c>
+      <c r="B134" t="n">
+        <v>852582.5</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>42529</v>
+      </c>
+      <c r="B135" t="n">
+        <v>860940.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/mexico_demanda_nacional_daily.xlsx
+++ b/output/mexico_demanda_nacional_daily.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B135"/>
+  <dimension ref="A1:B313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1604,6 +1604,1430 @@
         <v>860940.8</v>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>42530</v>
+      </c>
+      <c r="B136" t="n">
+        <v>865530.6</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>42531</v>
+      </c>
+      <c r="B137" t="n">
+        <v>864417.5</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>42532</v>
+      </c>
+      <c r="B138" t="n">
+        <v>817868.4</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>42533</v>
+      </c>
+      <c r="B139" t="n">
+        <v>746205.7</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>42534</v>
+      </c>
+      <c r="B140" t="n">
+        <v>843132.8</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>42535</v>
+      </c>
+      <c r="B141" t="n">
+        <v>866403.8</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>42536</v>
+      </c>
+      <c r="B142" t="n">
+        <v>873308.8</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>42537</v>
+      </c>
+      <c r="B143" t="n">
+        <v>877550.9</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>42538</v>
+      </c>
+      <c r="B144" t="n">
+        <v>874214.1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>42539</v>
+      </c>
+      <c r="B145" t="n">
+        <v>830824.6</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>42540</v>
+      </c>
+      <c r="B146" t="n">
+        <v>750654.7</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>42541</v>
+      </c>
+      <c r="B147" t="n">
+        <v>841078.6</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>42542</v>
+      </c>
+      <c r="B148" t="n">
+        <v>858583.7</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>42543</v>
+      </c>
+      <c r="B149" t="n">
+        <v>866935.1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>42544</v>
+      </c>
+      <c r="B150" t="n">
+        <v>872420.5</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>42545</v>
+      </c>
+      <c r="B151" t="n">
+        <v>868594</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>42546</v>
+      </c>
+      <c r="B152" t="n">
+        <v>833006.5</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>42547</v>
+      </c>
+      <c r="B153" t="n">
+        <v>767071.4</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>42548</v>
+      </c>
+      <c r="B154" t="n">
+        <v>854666</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>42549</v>
+      </c>
+      <c r="B155" t="n">
+        <v>869229.7</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>42550</v>
+      </c>
+      <c r="B156" t="n">
+        <v>866862</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>42551</v>
+      </c>
+      <c r="B157" t="n">
+        <v>868611.6</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>42552</v>
+      </c>
+      <c r="B158" t="n">
+        <v>869058.6</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>42553</v>
+      </c>
+      <c r="B159" t="n">
+        <v>826975.5</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>42554</v>
+      </c>
+      <c r="B160" t="n">
+        <v>764102.9</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>42555</v>
+      </c>
+      <c r="B161" t="n">
+        <v>764102.9</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>42556</v>
+      </c>
+      <c r="B162" t="n">
+        <v>869260.1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>42557</v>
+      </c>
+      <c r="B163" t="n">
+        <v>874416.1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>42558</v>
+      </c>
+      <c r="B164" t="n">
+        <v>884766.4</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>42559</v>
+      </c>
+      <c r="B165" t="n">
+        <v>887400.2</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>42560</v>
+      </c>
+      <c r="B166" t="n">
+        <v>849120.1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>42561</v>
+      </c>
+      <c r="B167" t="n">
+        <v>780402.4</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>42562</v>
+      </c>
+      <c r="B168" t="n">
+        <v>780402.4</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>42563</v>
+      </c>
+      <c r="B169" t="n">
+        <v>879563.4</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>42564</v>
+      </c>
+      <c r="B170" t="n">
+        <v>880543</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>42565</v>
+      </c>
+      <c r="B171" t="n">
+        <v>885499</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>42566</v>
+      </c>
+      <c r="B172" t="n">
+        <v>877375.5</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>42567</v>
+      </c>
+      <c r="B173" t="n">
+        <v>833556.1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>42568</v>
+      </c>
+      <c r="B174" t="n">
+        <v>764293.7</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>42569</v>
+      </c>
+      <c r="B175" t="n">
+        <v>858346.3</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>42570</v>
+      </c>
+      <c r="B176" t="n">
+        <v>876793.9</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>42571</v>
+      </c>
+      <c r="B177" t="n">
+        <v>877466.2</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>42572</v>
+      </c>
+      <c r="B178" t="n">
+        <v>876202.8</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>42573</v>
+      </c>
+      <c r="B179" t="n">
+        <v>875940.8</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>42574</v>
+      </c>
+      <c r="B180" t="n">
+        <v>836174.1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>42575</v>
+      </c>
+      <c r="B181" t="n">
+        <v>771198.5</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>42576</v>
+      </c>
+      <c r="B182" t="n">
+        <v>858297.4</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>42577</v>
+      </c>
+      <c r="B183" t="n">
+        <v>888326.2</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>42578</v>
+      </c>
+      <c r="B184" t="n">
+        <v>883463.9</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>42579</v>
+      </c>
+      <c r="B185" t="n">
+        <v>863547.7</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>42580</v>
+      </c>
+      <c r="B186" t="n">
+        <v>850848.8</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>42581</v>
+      </c>
+      <c r="B187" t="n">
+        <v>803438.4</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>42582</v>
+      </c>
+      <c r="B188" t="n">
+        <v>742227.9</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>42583</v>
+      </c>
+      <c r="B189" t="n">
+        <v>841023.7</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>42584</v>
+      </c>
+      <c r="B190" t="n">
+        <v>868107.4</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>42585</v>
+      </c>
+      <c r="B191" t="n">
+        <v>879274.7</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>42586</v>
+      </c>
+      <c r="B192" t="n">
+        <v>883783.3</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>42587</v>
+      </c>
+      <c r="B193" t="n">
+        <v>881091.8</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>42588</v>
+      </c>
+      <c r="B194" t="n">
+        <v>844442.3</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>42589</v>
+      </c>
+      <c r="B195" t="n">
+        <v>770543.6</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>42590</v>
+      </c>
+      <c r="B196" t="n">
+        <v>858492.1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>42591</v>
+      </c>
+      <c r="B197" t="n">
+        <v>874473.6</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>42592</v>
+      </c>
+      <c r="B198" t="n">
+        <v>878519.9</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>42593</v>
+      </c>
+      <c r="B199" t="n">
+        <v>883803.8</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>42594</v>
+      </c>
+      <c r="B200" t="n">
+        <v>884117</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>42595</v>
+      </c>
+      <c r="B201" t="n">
+        <v>837343.7</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>42596</v>
+      </c>
+      <c r="B202" t="n">
+        <v>750385.6</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>42597</v>
+      </c>
+      <c r="B203" t="n">
+        <v>830554.8</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>42598</v>
+      </c>
+      <c r="B204" t="n">
+        <v>849467.2</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>42599</v>
+      </c>
+      <c r="B205" t="n">
+        <v>847840.9</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>42600</v>
+      </c>
+      <c r="B206" t="n">
+        <v>855523.5</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>42601</v>
+      </c>
+      <c r="B207" t="n">
+        <v>860015.9</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>42602</v>
+      </c>
+      <c r="B208" t="n">
+        <v>818246.8</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>42603</v>
+      </c>
+      <c r="B209" t="n">
+        <v>743034.2</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>42604</v>
+      </c>
+      <c r="B210" t="n">
+        <v>815392.4</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>42605</v>
+      </c>
+      <c r="B211" t="n">
+        <v>815392.4</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>42606</v>
+      </c>
+      <c r="B212" t="n">
+        <v>849627.1</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>42607</v>
+      </c>
+      <c r="B213" t="n">
+        <v>854048.5</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>42608</v>
+      </c>
+      <c r="B214" t="n">
+        <v>851460.2</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>42609</v>
+      </c>
+      <c r="B215" t="n">
+        <v>816351.8</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>42610</v>
+      </c>
+      <c r="B216" t="n">
+        <v>743647.6</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>42611</v>
+      </c>
+      <c r="B217" t="n">
+        <v>833743.8</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>42612</v>
+      </c>
+      <c r="B218" t="n">
+        <v>851742.2</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>42613</v>
+      </c>
+      <c r="B219" t="n">
+        <v>850253.5</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>42614</v>
+      </c>
+      <c r="B220" t="n">
+        <v>848195.5</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>42615</v>
+      </c>
+      <c r="B221" t="n">
+        <v>847795.9</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>42616</v>
+      </c>
+      <c r="B222" t="n">
+        <v>808436.5</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>42617</v>
+      </c>
+      <c r="B223" t="n">
+        <v>730784.3</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>42618</v>
+      </c>
+      <c r="B224" t="n">
+        <v>812971.5</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>42619</v>
+      </c>
+      <c r="B225" t="n">
+        <v>822848.1</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>42620</v>
+      </c>
+      <c r="B226" t="n">
+        <v>828584.4</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>42621</v>
+      </c>
+      <c r="B227" t="n">
+        <v>841659.8</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>42622</v>
+      </c>
+      <c r="B228" t="n">
+        <v>849875.8</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>42623</v>
+      </c>
+      <c r="B229" t="n">
+        <v>814934.2</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>42624</v>
+      </c>
+      <c r="B230" t="n">
+        <v>748178.4</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>42625</v>
+      </c>
+      <c r="B231" t="n">
+        <v>834388</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>42626</v>
+      </c>
+      <c r="B232" t="n">
+        <v>857299.9</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>42627</v>
+      </c>
+      <c r="B233" t="n">
+        <v>852505.8</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>42628</v>
+      </c>
+      <c r="B234" t="n">
+        <v>827303</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>42629</v>
+      </c>
+      <c r="B235" t="n">
+        <v>748866</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>42630</v>
+      </c>
+      <c r="B236" t="n">
+        <v>765391.4</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>42631</v>
+      </c>
+      <c r="B237" t="n">
+        <v>741752.2</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>42632</v>
+      </c>
+      <c r="B238" t="n">
+        <v>841794.7</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>42633</v>
+      </c>
+      <c r="B239" t="n">
+        <v>858308.1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>42634</v>
+      </c>
+      <c r="B240" t="n">
+        <v>857722.4</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>42635</v>
+      </c>
+      <c r="B241" t="n">
+        <v>854291.4</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>42636</v>
+      </c>
+      <c r="B242" t="n">
+        <v>841051</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>42637</v>
+      </c>
+      <c r="B243" t="n">
+        <v>799315.7</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>42638</v>
+      </c>
+      <c r="B244" t="n">
+        <v>719368.2</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>42639</v>
+      </c>
+      <c r="B245" t="n">
+        <v>783363</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>42640</v>
+      </c>
+      <c r="B246" t="n">
+        <v>783246.2</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>42641</v>
+      </c>
+      <c r="B247" t="n">
+        <v>796990.6</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>42642</v>
+      </c>
+      <c r="B248" t="n">
+        <v>803403.2</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>42643</v>
+      </c>
+      <c r="B249" t="n">
+        <v>796194.8</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>42644</v>
+      </c>
+      <c r="B250" t="n">
+        <v>758399.1</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>42645</v>
+      </c>
+      <c r="B251" t="n">
+        <v>692480.8</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>42646</v>
+      </c>
+      <c r="B252" t="n">
+        <v>779128.4</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>42647</v>
+      </c>
+      <c r="B253" t="n">
+        <v>799950.7</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>42648</v>
+      </c>
+      <c r="B254" t="n">
+        <v>814197.8</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>42649</v>
+      </c>
+      <c r="B255" t="n">
+        <v>818861.3</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>42650</v>
+      </c>
+      <c r="B256" t="n">
+        <v>815801.9</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>42651</v>
+      </c>
+      <c r="B257" t="n">
+        <v>763459.9</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>42652</v>
+      </c>
+      <c r="B258" t="n">
+        <v>696875.4</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>42653</v>
+      </c>
+      <c r="B259" t="n">
+        <v>778619.8</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>42654</v>
+      </c>
+      <c r="B260" t="n">
+        <v>802778.2</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>42655</v>
+      </c>
+      <c r="B261" t="n">
+        <v>812367.1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>42656</v>
+      </c>
+      <c r="B262" t="n">
+        <v>822611.8</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>42657</v>
+      </c>
+      <c r="B263" t="n">
+        <v>818696.9</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>42658</v>
+      </c>
+      <c r="B264" t="n">
+        <v>779938.1</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>42659</v>
+      </c>
+      <c r="B265" t="n">
+        <v>716615.6</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>42660</v>
+      </c>
+      <c r="B266" t="n">
+        <v>801559.7</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>42661</v>
+      </c>
+      <c r="B267" t="n">
+        <v>818344.8</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>42662</v>
+      </c>
+      <c r="B268" t="n">
+        <v>824036.3</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>42663</v>
+      </c>
+      <c r="B269" t="n">
+        <v>824036.3</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>42664</v>
+      </c>
+      <c r="B270" t="n">
+        <v>788611.9</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>42665</v>
+      </c>
+      <c r="B271" t="n">
+        <v>744349.2</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>42666</v>
+      </c>
+      <c r="B272" t="n">
+        <v>681140.4</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>42667</v>
+      </c>
+      <c r="B273" t="n">
+        <v>772531.5</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>42668</v>
+      </c>
+      <c r="B274" t="n">
+        <v>794149.9</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>42669</v>
+      </c>
+      <c r="B275" t="n">
+        <v>803466.5</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n">
+        <v>42670</v>
+      </c>
+      <c r="B276" t="n">
+        <v>793559.6</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n">
+        <v>42671</v>
+      </c>
+      <c r="B277" t="n">
+        <v>782601.7</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n">
+        <v>42672</v>
+      </c>
+      <c r="B278" t="n">
+        <v>746380.1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n">
+        <v>42674</v>
+      </c>
+      <c r="B279" t="n">
+        <v>761118.2</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="n">
+        <v>42675</v>
+      </c>
+      <c r="B280" t="n">
+        <v>770432.9</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="n">
+        <v>42676</v>
+      </c>
+      <c r="B281" t="n">
+        <v>746965.4</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n">
+        <v>42677</v>
+      </c>
+      <c r="B282" t="n">
+        <v>779471.7</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="n">
+        <v>42678</v>
+      </c>
+      <c r="B283" t="n">
+        <v>769067.7</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="n">
+        <v>42679</v>
+      </c>
+      <c r="B284" t="n">
+        <v>726469.9</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="n">
+        <v>42680</v>
+      </c>
+      <c r="B285" t="n">
+        <v>668664.4</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="n">
+        <v>42681</v>
+      </c>
+      <c r="B286" t="n">
+        <v>751886.8</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="n">
+        <v>42682</v>
+      </c>
+      <c r="B287" t="n">
+        <v>759681.6</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="n">
+        <v>42683</v>
+      </c>
+      <c r="B288" t="n">
+        <v>751018.6</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="n">
+        <v>42684</v>
+      </c>
+      <c r="B289" t="n">
+        <v>743717.5</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="n">
+        <v>42685</v>
+      </c>
+      <c r="B290" t="n">
+        <v>739810.9</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="n">
+        <v>42686</v>
+      </c>
+      <c r="B291" t="n">
+        <v>699478.6</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="n">
+        <v>42687</v>
+      </c>
+      <c r="B292" t="n">
+        <v>631280.1</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="n">
+        <v>42688</v>
+      </c>
+      <c r="B293" t="n">
+        <v>712279.3</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="n">
+        <v>42689</v>
+      </c>
+      <c r="B294" t="n">
+        <v>737414</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="n">
+        <v>42690</v>
+      </c>
+      <c r="B295" t="n">
+        <v>739681.2</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="n">
+        <v>42691</v>
+      </c>
+      <c r="B296" t="n">
+        <v>738583.5</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="n">
+        <v>42692</v>
+      </c>
+      <c r="B297" t="n">
+        <v>737697</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="n">
+        <v>42693</v>
+      </c>
+      <c r="B298" t="n">
+        <v>689577.8</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="n">
+        <v>42694</v>
+      </c>
+      <c r="B299" t="n">
+        <v>615480.4</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="n">
+        <v>42695</v>
+      </c>
+      <c r="B300" t="n">
+        <v>615480.4</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="n">
+        <v>42696</v>
+      </c>
+      <c r="B301" t="n">
+        <v>707045</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="n">
+        <v>42697</v>
+      </c>
+      <c r="B302" t="n">
+        <v>707045</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="n">
+        <v>42698</v>
+      </c>
+      <c r="B303" t="n">
+        <v>733278.8</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="n">
+        <v>42699</v>
+      </c>
+      <c r="B304" t="n">
+        <v>729757.7</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="n">
+        <v>42700</v>
+      </c>
+      <c r="B305" t="n">
+        <v>690711.6</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="n">
+        <v>42701</v>
+      </c>
+      <c r="B306" t="n">
+        <v>633751.1</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="n">
+        <v>42702</v>
+      </c>
+      <c r="B307" t="n">
+        <v>714447.4</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="n">
+        <v>42703</v>
+      </c>
+      <c r="B308" t="n">
+        <v>738712.7</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="n">
+        <v>42704</v>
+      </c>
+      <c r="B309" t="n">
+        <v>741615.1</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="n">
+        <v>42705</v>
+      </c>
+      <c r="B310" t="n">
+        <v>735379.5</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="n">
+        <v>42706</v>
+      </c>
+      <c r="B311" t="n">
+        <v>735888.7</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="n">
+        <v>42707</v>
+      </c>
+      <c r="B312" t="n">
+        <v>704651.9</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="n">
+        <v>42708</v>
+      </c>
+      <c r="B313" t="n">
+        <v>642926.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/mexico_demanda_nacional_daily.xlsx
+++ b/output/mexico_demanda_nacional_daily.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B313"/>
+  <dimension ref="A1:B328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3028,6 +3028,126 @@
         <v>642926.5</v>
       </c>
     </row>
+    <row r="314">
+      <c r="A314" s="2" t="n">
+        <v>42714</v>
+      </c>
+      <c r="B314" t="n">
+        <v>694462.8</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="n">
+        <v>42715</v>
+      </c>
+      <c r="B315" t="n">
+        <v>630168.9</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="n">
+        <v>42716</v>
+      </c>
+      <c r="B316" t="n">
+        <v>660701.8</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="n">
+        <v>42717</v>
+      </c>
+      <c r="B317" t="n">
+        <v>719195.5</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="n">
+        <v>42718</v>
+      </c>
+      <c r="B318" t="n">
+        <v>743802.9</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="n">
+        <v>42719</v>
+      </c>
+      <c r="B319" t="n">
+        <v>745523.5</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="n">
+        <v>42720</v>
+      </c>
+      <c r="B320" t="n">
+        <v>745211.3</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="n">
+        <v>42721</v>
+      </c>
+      <c r="B321" t="n">
+        <v>709337.6</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="n">
+        <v>42722</v>
+      </c>
+      <c r="B322" t="n">
+        <v>709337.6</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="n">
+        <v>42723</v>
+      </c>
+      <c r="B323" t="n">
+        <v>724500.2</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="n">
+        <v>42725</v>
+      </c>
+      <c r="B324" t="n">
+        <v>736001.6</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="n">
+        <v>42726</v>
+      </c>
+      <c r="B325" t="n">
+        <v>724659.1</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="n">
+        <v>42727</v>
+      </c>
+      <c r="B326" t="n">
+        <v>704022.2</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="n">
+        <v>42728</v>
+      </c>
+      <c r="B327" t="n">
+        <v>621386.7</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="n">
+        <v>42792</v>
+      </c>
+      <c r="B328" t="n">
+        <v>648602.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
